--- a/data_extactor/batch_10_fa/batch_0066_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0066_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | مانیتورینگ | ریاضیات | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | امنیت و ایمنی عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | سهولت در کار با اعداد | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | بینایی نزدیک | توجه انتخابی | درک کتبی | بیان کتبی | استدلال ریاضی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری مقوله‌ای | استدلال استقرایی</t>
+          <t>درک شفاهی | توانایی عددی | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | درک کتبی | بیان کتبی | استدلال ریاضی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | گفتگوهای تلفنی | ایمیل | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | نزدیکی فیزیکی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان به صورت ایستاده | فشار زمانی</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | صندوق‌داران | کارمندان باجه و اجاره | تحلیل‌گران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مدیران مالی | کارکنان باجه قمارخانه | تعویض‌کنندگان پول قمارخانه و صندوق‌داران باجه | مصاحبه‌کنندگان و کارمندان وام | کارشناسان تسهیلات | کارمندان افتتاح حساب جدید | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | صندوق‌داران | کارمندان باجه و اجاره | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مدیران مالی | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتریان و شخصی | کامپیوتر و الکترونیک | امور اداری و مدیریت | قانون و حکومت</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری مقوله‌ای | اشتراک زمانی | زبردستی انگشتان | زبردستی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها | استدلال ریاضی | سهولت در کار با اعداد | سرعت ادراکی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | استدلال ریاضی | توانایی عددی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان به صورت نشسته | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارمندان دفترداری، حسابداری و حسابرسی | کارمندان صدور صورتحساب و ثبت | وصول‌کنندگان قبوض و حساب‌ها | کارمندان حقوق و دستمزد و ثبت زمان | کارمندان تدارکات | تحویل‌داران | کارمندان کارگزاری | کارمندان افتتاح حساب جدید | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان و کارمندان وام | کارکنان باجه قمارخانه | کارمندان پردازش بیمه و خسارت | دستیاران آماری | اپراتورهای ورود داده | کارمندان دفتری عمومی | توزین‌کنندگان، اندازه‌گیران، بررسی‌کنندگان و نمونه‌برداران، ثبت سوابق | حسابداران و حسابرسان | تحلیل‌گران بودجه | متخصصان مالی، همه موارد دیگر | سرپرستان رده اول کارکنان دفتری و پشتیبانی اداری</t>
+          <t>کارمندان دفترداری، حسابداری و حسابرسی | کارمندان صدور صورتحساب و ثبت | وصول‌کنندگان قبوض و حساب‌ها | کارمندان حقوق و دستمزد و ثبت زمان | کارمندان تدارکات | تحویل‌داران | کارمندان کارگزاری | کارمندان حساب‌های جدید | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان و کارمندان وام | کارکنان باجه قمارخانه | کارمندان پردازش بیمه و بیمه‌نامه | دستیاران آماری | اپراتورهای ورود داده | کارمندان دفتری عمومی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | حسابداران و حسابرسان | تحلیلگران بودجه | متخصصان مالی، سایر | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت حساب | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Bloomberg Professional | HEAT Software GoldMine | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual FoxPro | Microsoft Word | نرم‌افزار معاملات آنلاین | Oracle PeopleSoft | Royal Alliance VISION2020 Core | نرم‌افزار Salesforce | نرم‌افزار برنامه‌ریزی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار پردازش تراکنش | نرم‌افزار مرورگر وب | WiredRed Software e/pop Basic</t>
+          <t>نرم‌افزار مدیریت حساب | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Bloomberg Professional | HEAT Software GoldMine | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual FoxPro | Microsoft Word | نرم‌افزار معاملات آنلاین | Oracle PeopleSoft | Royal Alliance VISION2020 Core | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار پردازش تراکنش | نرم‌افزار مرورگر وب | WiredRed Software e/pop Basic</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی | ریاضیات | کامپیوتر و الکترونیک | اقتصاد و حسابداری | اداری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | سهولت در کار با اعداد | استدلال ریاضی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | تماس با دیگران | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | فشار زمانی | محیط داخلی، کنترل‌شده از نظر دما | اهمیت تکرار وظایف یکسان | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی</t>
+          <t>ایمیل | مکالمات تلفنی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تحلیل‌گران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و خسارت | مصاحبه‌کنندگان و کارمندان وام | کارشناسان تسهیلات | تحلیل‌گران مدیریت | کارمندان افتتاح حساب جدید | کارمندان دفتری عمومی | مشاوران مالی شخصی | کارمندان تدارکات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی | تحویل‌داران</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | مشاوران مالی شخصی | کارمندان تدارکات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار پرونده الکترونیک سلامت EHR | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | نرم‌افزار تصویربرداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | نرم‌افزار SAP</t>
+          <t>نرم‌افزار تبادل الکترونیکی داده EDI | نرم‌افزار پرونده الکترونیک سلامت EHR | Epic Systems | GE Healthcare Centricity EMR | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار تصویربرداری | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | خدمات مشتریان و شخصی | اقتصاد و حسابداری | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی به اطلاعات | تشخیص گفتار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری مقوله‌ای | روان بودن ایده‌ها</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | تماس با دیگران | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | گفتگوهای تلفنی | صرف زمان به صورت نشسته | اهمیت تکرار وظایف یکسان | تعیین وظایف, اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، کنترل‌شده از نظر دما | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فشار زمانی | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | گزارشگران دادگاه و پیاده‌سازان همزمان گفتار | کارمندان دادگاه، شهرداری و مجوز | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | متخصصان مدیریت اسناد | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | کارمندان پردازش بیمه و خسارت | مصاحبه‌کنندگان، به جز واجد شرایط بودن و وام | منشی‌های حقوقی و دستیاران اداری | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری</t>
+          <t>مدیران خدمات اداری | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | متخصصان مدیریت اسناد | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abilis CORIS Offender Management System | Adobe Acrobat | Corel WordPerfect Office Suite | Data Technologies Summit | نرم‌افزار ایمیل | IBM Judicial Enforcement Management System JEMS | IBM Notes | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | برنامه‌های صفحه‌گسترده | Syscon Court Clerk | Thomson Reuters Westlaw | نرم‌افزار برنامه‌ریزی کاری | Zoom</t>
+          <t>Abilis CORIS Offender Management System | Adobe Acrobat | Corel WordPerfect Office Suite | Data Technologies Summit | نرم‌افزار ایمیل | IBM Judicial Enforcement Management System JEMS | IBM Notes | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | برنامه‌های صفحه‌گسترده | Syscon Court Clerk | Thomson Reuters Westlaw | نرم‌افزار زمان‌بندی کار | Zoom</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | قانون و حکومت | زبان انگلیسی | امور اداری و مدیریت | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | قانون و دولت | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی به اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری مقوله‌ای</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | تماس با دیگران | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | ایمیل | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، کنترل‌شده از نظر دما | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>قضات قانون اداری، دادرسان و ماموران رسیدگی | مدیران خدمات اداری | ماموران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و پیاده‌سازان همزمان گفتار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان رده اول کارکنان دفتری و پشتیبانی اداری | کارمندان پردازش بیمه و خسارت | قضات، قضات صلح و دادرسان | دستیاران قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | کارمندان دفتری عمومی | دستیاران حقوقی و دستیاران قانون | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | ممیزان سند، خلاصه‌نویسان و جستجوگران</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران خدمات اداری | افسران انطباق | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پردازش بیمه و بیمه‌نامه | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | کارمندان دفتری عمومی | پارالیگال‌ها و دستیاران حقوقی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | مانیتورینگ</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ریاضیات | قانون و حکومت | اداری | اقتصاد و حسابداری | کامپیوتر و الکترونیک | امور اداری و مدیریت</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | قانون و دولت | اداری | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | ترتیب‌دهی به اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | تماس با دیگران | ایمیل | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | صرف زمان به صورت نشسته | فشار زمانی | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | موقعیت‌های تعارض | محیط داخلی، کنترل‌شده از نظر دما | صرف زمان برای انجام حرکات تکراری | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | موقعیت‌های تعارض | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | تحلیل‌گران اعتبار | مشاوران اعتبار | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارمندان پردازش بیمه و خسارت | مصاحبه‌کنندگان و کارمندان وام | کارشناسان تسهیلات | کارمندان افتتاح حساب جدید | مشاوران مالی شخصی | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی | تحویل‌داران</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | تحلیلگران اعتبار | مشاوران اعتبار | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تحویل‌داران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | AS/400 Database | Active Data Online WebChat | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe Photoshop | Airtable | Apple Keynote | Apple macOS | Applied Systems Vision | Astute Solutions PowerCenter | Austin Logistics CallSelect | Austin Logistics CallTech | Austin Logistics Valeo | Avidian Technologies Prophet | Blackbaud The Raiser's Edge | نرم‌افزار رایانش ابری Citrix | نرم‌افزار مدیریت حساب مشتری | نرم‌افزار مدیریت تیکت شکایات مشتری | نرم‌افزار خدمات و پشتیبانی مشتری | نرم‌افزار تولید دانش خدمات مشتری | DSC Pacer Interactive Voice Response System | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | FaceTime | Facebook | FileMaker Pro | نرم‌افزار حسابداری وجوه | Google Docs | Google Drive | Google Meet | Google Sites | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | Hosted Support ezSupport Pro | سیستم مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | LogMeIn GoToMeeting | Lynk Everest | نرم‌افزار MEDITECH | Main Street Softworks Monetra | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Windows | Microsoft Word | نرم‌افزار مرکز تماس چندکاناله | Nearpod | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Open Text Fax Server, RightFax Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Taleo | Padlet | Parature eRealtime | Parature eTicket | Poll Everywhere | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage MAS 200 ERP | نرم‌افزار اتوماسیون نیروی فروش | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | ShoreTel | Skype | Slack | سایت‌های رسانه‌های اجتماعی | نرم‌افزار Stamps.com | SugarSync | نرم‌افزار مالیات | Telemation e-CRM | Timpani Chat | Timpani Contact Center | Timpani Email | نرم‌افزار پیام‌رسانی یکپارچه | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار Yardi | YouTube | Zoom | eStara Softphone | iShip | j2 Global Communications onebox</t>
+          <t>ADP Workforce Now | AS/400 Database | Active Data Online WebChat | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe Photoshop | Airtable | Apple Keynote | Apple macOS | Applied Systems Vision | Astute Solutions PowerCenter | Austin Logistics CallSelect | Austin Logistics CallTech | Austin Logistics Valeo | Avidian Technologies Prophet | Blackbaud The Raiser's Edge | نرم‌افزار رایانش ابری Citrix | نرم‌افزار مدیریت حساب مشتری | نرم‌افزار مدیریت تیکت شکایات مشتری | نرم‌افزار خدمات و پشتیبانی مشتری | نرم‌افزار تولید دانش خدمات مشتری | DSC Pacer Interactive Voice Response System | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | FaceTime | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | Google Docs | Google Drive | Google Meet | Google Sites | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hosted Support ezSupport Pro | نرم‌افزار مدیریت منابع انسانی HRMS | IBM Cognos Impromptu | IBM Domino | IBM Notes | نرم‌افزار IBM Power Systems | Intuit QuickBooks | Kronos Workforce Timekeeper | LexisNexis | LinkedIn | LogMeIn GoToMeeting | Lynk Everest | نرم‌افزار MEDITECH | Main Street Softworks Monetra | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Windows | Microsoft Word | نرم‌افزار مرکز تماس چندکاناله | Nearpod | NetSuite ERP | نرم‌افزار امنیت سایبری NortonLifeLock | Open Text Fax Server, RightFax Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Taleo | Padlet | Parature eRealtime | Parature eTicket | Poll Everywhere | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | Sage 50 Accounting | Sage MAS 200 ERP | نرم‌افزار اتوماسیون نیروی فروش | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | ShoreTel | Skype | Slack | سایت‌های رسانه‌های اجتماعی | نرم‌افزار Stamps.com | SugarSync | نرم‌افزار مالیاتی | Telemation e-CRM | Timpani Chat | Timpani Contact Center | Timpani Email | نرم‌افزار پیام‌رسانی یکپارچه | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار Yardi | YouTube | Zoom | eStara Softphone | iShip | j2 Global Communications onebox</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امور اداری و مدیریت | فروش و بازاریابی | ریاضیات | اداری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | فروش و بازاریابی | ریاضیات | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی به اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | تماس با دیگران | محیط داخلی، کنترل‌شده از نظر دما | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | فشار زمانی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | ایمیل | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | صندوق‌داران | کارمندان مکاتبات | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان دفتری و پشتیبانی اداری | کارمندان پردازش بیمه و خسارت | نمایندگان فروش بیمه | تحلیل‌گران مدیریت | کارمندان افتتاح حساب جدید | کارمندان دفتری عمومی | کارمندان ثبت سفارش | پذیرش‌کنندگان و کارمندان اطلاعات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازاریابان تلفنی | تحویل‌داران</t>
+          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان کارگزاری | صندوق‌داران | کارمندان مکاتبات | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | کارمندان ثبت سفارش | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازاریابان تلفنی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | مانیتورینگ</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امور اداری و مدیریت | اداری | پرسنل و منابع انسانی | آموزش و پرورش | کامپیوتر و الکترونیک | ریاضیات | قانون و حکومت | امنیت و ایمنی عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات | قانون و دولت | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری مقوله‌ای</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | تماس با دیگران | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، کنترل‌شده از نظر دما | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | ارتباط با دیگران | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | ارزیابان، بررسی‌کنندگان و محققان خسارت | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | ماموران انطباق | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مشاوران و راهنمایان تحصیلی، حرفه‌ای و شغلی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان پردازش بیمه و خسارت | مصاحبه‌کنندگان، به جز واجد شرایط بودن و وام | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | نمایندگان بیمار | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | ممیزان و وصول‌کنندگان مالیات، و ماموران دارایی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | افسران انطباق | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مشاوران و راهنمایان آموزشی، شغلی و تحصیلی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان پردازش بیمه و بیمه‌نامه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | نمایندگان بیمار | مشاوران توانبخشی | مدیران خدمات اجتماعی و جامعه | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | مانیتورینگ | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری | زبان انگلیسی | خدمات مشتریان و شخصی | قانون و حکومت | کامپیوتر و الکترونیک | مخابرات | ریاضیات | امنیت و ایمنی عمومی</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | مخابرات | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی به اطلاعات | درک کتبی | انعطاف‌پذیری مقوله‌ای | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | توجه انتخابی | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | حساسیت به مسئله | روان بودن ایده‌ها</t>
+          <t>ترتیب‌دهی اطلاعات | درک کتبی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | توجه انتخابی | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | تماس با دیگران | ایمیل | صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | محیط داخلی، کنترل‌شده از نظر دما | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | آرشیویست‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان مکاتبات | گزارشگران دادگاه و پیاده‌سازان همزمان گفتار | کارمندان دادگاه، شهرداری و مجوز | اپراتورهای ورود داده | متخصصان مدیریت اسناد | متخصصان فناوری اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | تفکیک‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین پردازش پست اداره پست | پذیرش‌کنندگان و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | ممیزان سند، خلاصه‌نویسان و جستجوگران | پردازش‌کنندگان کلمات و تایپیست‌ها</t>
+          <t>مدیران خدمات اداری | آرشیوچی‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | اپراتورهای ورود داده | متخصصان مدیریت اسناد | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران آماری | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | مانیتورینگ | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | امنیت و ایمنی عمومی | اداری | کامپیوتر و الکترونیک | امور اداری و مدیریت | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | انعطاف‌پذیری مقوله‌ای | ترتیب‌دهی به اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>تماس با دیگران | گفتگوهای تلفنی | بحث‌های چهره‌به‌چهره با افراد و در گروه‌ها | کار با یا مشارکت در یک گروه کاری یا team | سروکار داشتن با مشتریان خارجی یا عموم مردم به‌طور کلی | ایمیل | محیط داخلی، کنترل‌شده از نظر دما | فراوانی تصمیم‌گیری | سروکار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | اهمیت تکرار وظایف یکسان | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | اهمیت تکرار وظایف یکسان | موقعیت‌های تعارض | صرف زمان برای انجام حرکات تکراری | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باربران چمدان و پادوها | صندوق‌داران | راهنمایان مهمانان | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | سرپرستان رده اول کارکنان خانه‌داری و سرایداری | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | خدمتکاران و نظافتچی‌های خانه‌داری | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | متصدیان پارکینگ | متصدیان مسافران | پذیرش‌کنندگان و کارمندان اطلاعات | نمایندگان رزرو و بلیط حمل‌ونقل و کارمندان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها | گارسون‌ها</t>
+          <t>باربران چمدان و پادوهای هتل | صندوق‌داران | کانسرج‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سروکنندگان غذا، غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | خدمتکاران و تمیزکنندگان خانه‌داری | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | متصدیان پارکینگ | متصدیان مسافران | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0066_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0066_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | ریاضیات | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | مهارت در کار با اعداد | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | توجه انتخابی | درک کتبی | بیان کتبی | استدلال ریاضی | استدلال قیاسی | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی</t>
+          <t>درک شفاهی | توانایی عددی | تشخیص گفتار | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه انتخابی | درک کتبی | بیان کتبی | استدلال ریاضی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان معاملات کارگزاری | صندوق‌داران | متصدیان باجه و کرایه تجهیزات | کارشناسان تحلیل اعتبار و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات مشتریان | مدیران مالی | کارشناسان تسویه و خزانه‌داری اماکن تفریحی | صندوق‌داران باجه‌های تفریحی | کارشناسان مصاحبه و بررسی وام | کارشناسان اعطای تسهیلات | کارشناسان افتتاح حساب | متصدیان امور اداری و دفتری عمومی | کارشناسان حقوق و دستمزد و ثبت کارکرد | کارشناسان فروش خدمات (به‌جز بیمه، املاک، مالی و تبلیغات) | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | مدیران امور مالی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و امور دولتی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به‌خاطرسپاری | روانی ایده‌ها | استدلال ریاضی | مهارت در کار با اعداد | سرعت ادراک</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | استدلال ریاضی | توانایی عددی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کارشناسان وصول مطالبات | کارشناسان حقوق و دستمزد و ثبت کارکرد | کارشناسان کارپردازی و خرید | تحویل‌داران و متصدیان امور بانکی | کارشناسان معاملات کارگزاری | کارشناسان افتتاح حساب | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان مصاحبه و بررسی وام | کارشناسان تسویه و خزانه‌داری اماکن تفریحی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | دستیاران و تحلیل‌گران آمار | متصدیان ورود داده‌ها و اطلاعات | متصدیان امور اداری و دفتری عمومی | متصدیان ثبت، اندازه‌گیری و نمونه‌گیری | حسابداران و حسابرسان | تحلیل‌گران بودجه | کارشناسان و متخصصان امور مالی، سایر مشاغل | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
+          <t>کارمندان دفترداری، حسابداری و امور حسابرسی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان امور حقوق، دستمزد و ثبت زمان | کارمندان تدارکات و کارپردازی | تحویل‌داران و متصدیان امور بانکی | کارشناسان امور اداری و معاملات کارگزاری | متصدیان افتتاح حساب | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان پذیرش و امور اداری تسهیلات و وام | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | دستیاران و تکنسین‌های آمار | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | حسابداران و حسابرسان | تحلیل‌گران بودجه | سایر کارشناسان و متخصصان امور مالی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری و سازمانی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | مهارت در کار با اعداد | استدلال ریاضی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | استدلال قیاسی | توجه انتخابی | توانایی عددی | استدلال ریاضی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان تحلیل اعتبار و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات مشتریان | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | کارشناسان مصاحبه و بررسی وام | کارشناسان اعطای تسهیلات | تحلیل‌گران مدیریت و فرآیندها | کارشناسان افتتاح حساب | متصدیان امور اداری و دفتری عمومی | مشاوران مدیریت ثروت و سرمایه‌گذاری فردی | کارشناسان کارپردازی و خرید | کارشناسان فروش خدمات (به‌جز بیمه، املاک، مالی و تبلیغات) | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | مشاوران مالی فردی | کارمندان تدارکات و کارپردازی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نگارش | درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>اداری و سازمانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | دید نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها</t>
+          <t>بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان وصول مطالبات | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کاردان‌ها و کارشناسان حسابداری و حسابرسی | تندنویسان و گزارشگران جلسات و دادگاه | متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و صدور پروانه | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات مشتریان | کارشناسان مدیریت اسناد و مدارک | ارزیابان واجدین شرایط برنامه‌های دولتی | مسئولان دفاتر و دستیاران اجرایی مدیران ارشد | متصدیان بایگانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | متصدیان مصاحبه و پرسشگری (به‌جز واجدین شرایط و وام) | منشی‌ها و مسئولان دفاتر حقوقی | متصدیان امور اداری و دفتری عمومی | کارشناسان حقوق و دستمزد و ثبت کارکرد | مسئولان پذیرش و راهنمای مراجعان | منشی‌ها و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | دستیاران و تحلیل‌گران آمار</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مدیریت اسناد و مدارک | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | کارمندان پردازش خسارت و بیمه‌نامه‌ها | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری دفاتر حقوقی | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اداری و سازمانی | حقوق و امور دولتی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | قانون و دولت | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، داوران و دادرسی‌کنندگان | مدیران خدمات اداری | کارشناسان نظارت و انطباق با قوانین و مقررات | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و گزارشگران جلسات و دادگاه | ارزیابان واجدین شرایط برنامه‌های دولتی | مسئولان دفاتر و دستیاران اجرایی مدیران ارشد | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | قضات، دادیاران و بازپرسان | پژوهشگران و دستیاران قضایی | وکلا و حقوق‌دانان | منشی‌ها و مسئولان دفاتر حقوقی | متصدیان امور اداری و دفتری عمومی | دستیاران حقوقی و کارشناسان پشتیبانی امور وکالت | مسئولان پذیرش و راهنمای مراجعان | منشی‌ها و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | ممیزان، وصول‌کنندگان و ماموران مالیاتی | کارشناسان بررسی و جستجوی اسناد مالکیت و ثبتی</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران خدمات اداری و پشتیبانی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان و دستیاران امور حقوقی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | نظارت</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | حقوق و امور دولتی | اداری و سازمانی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | قانون و دولت | اداری | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | دید نزدیک | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان تحلیل اعتبار و تسهیلات | مشاوران امور اعتباری و تسهیلات | کارشناسان خدمات مشتریان | ارزیابان واجدین شرایط برنامه‌های دولتی | بازرسان و ممیزان امور مالی | مدیران مالی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | کارشناسان مصاحبه و بررسی وام | کارشناسان اعطای تسهیلات | کارشناسان افتتاح حساب | مشاوران مدیریت ثروت و سرمایه‌گذاری فردی | کارگزاران و نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | ممیزان، وصول‌کنندگان و ماموران مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تحلیل‌گران اعتبارات و تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | فروش و بازاریابی | ریاضیات | اداری و سازمانی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | فروش و بازاریابی | ریاضیات | اداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | دید نزدیک | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارشناسان وصول مطالبات | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کارشناسان معاملات کارگزاری | صندوق‌داران | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان باجه و کرایه تجهیزات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | ارزیابان واجدین شرایط برنامه‌های دولتی | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | نمایندگان فروش بیمه | تحلیل‌گران مدیریت و فرآیندها | کارشناسان افتتاح حساب | متصدیان امور اداری و دفتری عمومی | کارشناسان ثبت سفارش‌ها | مسئولان پذیرش و راهنمای مراجعان | کارشناسان فروش خدمات (به‌جز بیمه، املاک، مالی و تبلیغات) | بازاریابان تلفنی | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارشناسان امور اداری و معاملات کارگزاری | صندوق‌داران | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان باجه و کرایه کالا و خدمات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان بازاریابی تلفنی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | اداری و سازمانی | پرسنلی و منابع انسانی | آموزش و تدریس | رایانه و الکترونیک | ریاضیات | حقوق و امور دولتی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اداری | پرسنل و منابع انسانی | آموزش و پرورش | رایانه و الکترونیک | ریاضیات | قانون و دولت | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدارس | ارزیابان، کارشناسان و محققان خسارت بیمه | مدیران جبران خدمت و مزایا | متخصصان جبران خدمت، مزایا و تجزیه و تحلیل شغل | کارشناسان نظارت و انطباق با قوانین و مقررات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران امور اعتباری و تسهیلات | کارشناسان خدمات مشتریان | مشاوران و راهنمایان تحصیلی، تربیتی و شغلی | دستیاران منابع انسانی (به‌جز حقوق و دستمزد و ثبت کارکرد) | کارشناسان منابع انسانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه | متصدیان مصاحبه و پرسشگری (به‌جز واجدین شرایط و وام) | منشی‌ها و مسئولان دفاتر حقوقی | تحلیل‌گران مدیریت و فرآیندها | متصدیان امور اداری و دفتری عمومی | نمایندگان و مدافعان حقوق بیماران | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و توان‌بخشی جامعه‌محور | ممیزان، وصول‌کنندگان و ماموران مالیاتی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | مشاوران تحصیلی، شغلی و هدایت استعدادها | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری | کارشناسان امور بیماران و پذیرش | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>اداری و سازمانی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و امور دولتی | رایانه و الکترونیک | مخابرات و ارتباطات | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | رایانه و الکترونیک | مخابرات | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | درک کتبی | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | توجه انتخابی | سرعت ادراک | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری انسداد | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها</t>
+          <t>ترتیب‌دهی اطلاعات | درک کتبی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | درک شفاهی | بیان شفاهی | بیان کتبی | توجه انتخابی | سرعت ادراکی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | حساسیت به مسئله | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | آرشیویست‌ها و کارشناسان مراکز اسناد | کارشناسان صدور صورت‌حساب و ثبت اسناد مالی | کاردان‌ها و کارشناسان حسابداری و حسابرسی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و گزارشگران جلسات و دادگاه | متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و صدور پروانه | متصدیان ورود داده‌ها و اطلاعات | کارشناسان مدیریت اسناد و مدارک | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران مدیریت و فرآیندها | متخصصان اسناد و مدارک پزشکی | متصدیان امور اداری و دفتری عمومی | کارشناسان حقوق و دستمزد و ثبت کارکرد | متصدیان دسته‌بندی و ماشین‌آلات پردازش پستی | مسئولان پذیرش و راهنمای مراجعان | منشی‌ها و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | دستیاران و تحلیل‌گران آمار | کارشناسان بررسی و جستجوی اسناد مالکیت و ثبتی | پردازشگران متون و تایپیست‌ها</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارشناسان اسناد و آرشیو | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان مدیریت اسناد و مدارک | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | اپراتورها و متصدیان تفکیک و پردازش پستی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | دستیاران و تکنسین‌های آمار | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | اداری و سازمانی | رایانه و الکترونیک | مدیریت و امور اداری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | اداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>باربران و پادوهای هتل | صندوق‌داران | دربانان مجلل و راهنمایان اختصاصی میهمانان در هتل | متصدیان باجه و کرایه تجهیزات | کارشناسان خدمات مشتریان | سالن‌داران، متصدیان بوفه و کمکی‌های کافه‌تریا | سرپرستان رده‌اول کارکنان خدمات و نظافت | مهمانداران و توزیع‌کنندگان غذا در محیط‌های غیررستورانی | میزبانان رستوران، سالن و کافی‌شاپ | متصدیان رختکن، اتاق لباس و اماکن ورزشی | مدیران اقامتی و هتلداری | خدمتکاران و نظافتچیان اماکن اقامتی | منشی‌ها و مسئولان دفاتر پزشکی | متصدیان امور اداری و دفتری عمومی | متصدیان پارک خودرو | راهنمایان و متصدیان خدمات مسافران | مسئولان پذیرش و راهنمای مراجعان | متصدیان صدور بلیط، خدمات مسافرتی و رزرواسیون | راهنمایان سالن‌ها، لابی و کنترل‌کنندگان بلیط | گارسون‌ها و پیشخدمت‌های رستوران</t>
+          <t>متصدیان حمل بار و خدمات هتل | صندوق‌داران | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سروکنندگان غذا در محیط‌های غیررستورانی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان رختکن، امانات و اتاق پرو | مدیران هتل و مراکز اقامتی | خدمتکاران و نظافتچیان منازل و هتل‌ها | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنماها، متصدیان سالن و بلیط‌گیرها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
